--- a/dist/Premium_Wedding_Planner_BLANK.xlsx
+++ b/dist/Premium_Wedding_Planner_BLANK.xlsx
@@ -3213,42 +3213,42 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
           <t>1. Start on the Settings sheet — enter your names, wedding date, budget and guest target once.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="B8" s="6" t="inlineStr">
         <is>
           <t>2. Every other sheet (Dashboard, Budget, Guest List, Checklist and more) calculates automatically from what you enter.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9" ht="34" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
           <t>3. Use the dropdown menus in colored-header columns to keep your data consistent — just click a cell and choose from the list.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="6" t="inlineStr">
         <is>
           <t>4. Visit the Dashboard any time for a beautiful, real-time snapshot of your whole wedding.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="6" t="inlineStr">
         <is>
           <t>5. Each sheet has a small navigation link at the top-left to jump back to the Dashboard or this page.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
           <t>6. All key sheets are print-ready — use File &gt; Print, and each will fit neatly on the page.</t>
@@ -12113,7 +12113,7 @@
       <c r="C68" s="19" t="n"/>
       <c r="D68" s="20" t="n"/>
       <c r="E68" s="36">
-        <f>COUNTIF(I6:I65,"Attending")+COUNTIFS(I6:I65,"Attending",J6:J65,"Yes")</f>
+        <f>COUNTIF(I6:I65,"Attending")</f>
         <v/>
       </c>
       <c r="F68" s="19" t="n"/>
